--- a/astro-site/public/dl/kit-tareas-catering/06-eventos-festivos.xlsx
+++ b/astro-site/public/dl/kit-tareas-catering/06-eventos-festivos.xlsx
@@ -1,19 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Bodas" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Corporativo" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Cocktail Standing" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Outdoor - Exterior" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bodas" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corporativo" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cocktail Standing" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Outdoor - Exterior" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Bodas'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Corporativo'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Cocktail Standing'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Outdoor - Exterior'!$5:$5</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -21,7 +26,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -82,6 +87,11 @@
       <name val="Calibri"/>
       <color rgb="00999999"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="9">
@@ -158,60 +168,71 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="21">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="5" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="6" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="7" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="8" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C8E6C9"/>
+          <bgColor rgb="00C8E6C9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -571,15 +592,16 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B11"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="3"/>
-    <col customWidth="1" max="2" min="2" width="80"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -587,6 +609,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -615,9 +638,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="B8" t="inlineStr"/>
-    </row>
+    <row r="8"/>
     <row r="9">
       <c r="B9" s="2" t="inlineStr">
         <is>
@@ -639,8 +660,25 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-catering · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -649,18 +687,18 @@
   <sheetPr>
     <tabColor rgb="00E0F2F1"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -677,6 +715,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -835,6 +874,7 @@
       <c r="F11" s="11" t="n"/>
       <c r="G11" s="13" t="n"/>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
@@ -992,6 +1032,26 @@
       <c r="E20" s="12" t="n"/>
       <c r="F20" s="11" t="n"/>
       <c r="G20" s="13" t="n"/>
+    </row>
+    <row r="21">
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C21">
+        <f>COUNTIF(E6:E20,"✓")</f>
+        <v>1.0</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E21">
+        <f>COUNTIF(B6:B20,"?*")</f>
+        <v>13.0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="16" t="inlineStr">
@@ -1016,12 +1076,26 @@
     <mergeCell ref="A13:G13"/>
     <mergeCell ref="A22:G22"/>
   </mergeCells>
+  <conditionalFormatting sqref="A6:G20">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$E6="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="E6 E7 E8 E9 E10 E11 E15 E16 E17 E18 E19 E20" type="list">
+    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E15 E16 E17 E18 E19 E20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
       <formula1>"✓,✗,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1030,18 +1104,18 @@
   <sheetPr>
     <tabColor rgb="00FFF8E1"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1058,6 +1132,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -1197,6 +1272,7 @@
       <c r="F10" s="11" t="n"/>
       <c r="G10" s="13" t="n"/>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
@@ -1335,6 +1411,26 @@
       <c r="E18" s="12" t="n"/>
       <c r="F18" s="11" t="n"/>
       <c r="G18" s="13" t="n"/>
+    </row>
+    <row r="19">
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C19">
+        <f>COUNTIF(E6:E18,"✓")</f>
+        <v>1.0</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E19">
+        <f>COUNTIF(B6:B18,"?*")</f>
+        <v>11.0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="16" t="inlineStr">
@@ -1359,12 +1455,26 @@
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A21:G21"/>
   </mergeCells>
+  <conditionalFormatting sqref="A6:G18">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$E6="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="E6 E7 E8 E9 E10 E14 E15 E16 E17 E18" type="list">
+    <dataValidation sqref="E6 E7 E8 E9 E10 E14 E15 E16 E17 E18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
       <formula1>"✓,✗,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1373,18 +1483,18 @@
   <sheetPr>
     <tabColor rgb="00E8F5E9"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1401,6 +1511,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -1540,6 +1651,7 @@
       <c r="F10" s="11" t="n"/>
       <c r="G10" s="13" t="n"/>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
@@ -1678,6 +1790,26 @@
       <c r="E18" s="12" t="n"/>
       <c r="F18" s="11" t="n"/>
       <c r="G18" s="13" t="n"/>
+    </row>
+    <row r="19">
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C19">
+        <f>COUNTIF(E6:E18,"✓")</f>
+        <v>1.0</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E19">
+        <f>COUNTIF(B6:B18,"?*")</f>
+        <v>11.0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="16" t="inlineStr">
@@ -1702,12 +1834,26 @@
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A21:G21"/>
   </mergeCells>
+  <conditionalFormatting sqref="A6:G18">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$E6="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="E6 E7 E8 E9 E10 E14 E15 E16 E17 E18" type="list">
+    <dataValidation sqref="E6 E7 E8 E9 E10 E14 E15 E16 E17 E18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
       <formula1>"✓,✗,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1716,18 +1862,18 @@
   <sheetPr>
     <tabColor rgb="00E0F2F1"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1744,6 +1890,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -1902,6 +2049,7 @@
       <c r="F11" s="11" t="n"/>
       <c r="G11" s="13" t="n"/>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
@@ -2059,6 +2207,26 @@
       <c r="E20" s="12" t="n"/>
       <c r="F20" s="11" t="n"/>
       <c r="G20" s="13" t="n"/>
+    </row>
+    <row r="21">
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C21">
+        <f>COUNTIF(E6:E20,"✓")</f>
+        <v>1.0</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E21">
+        <f>COUNTIF(B6:B20,"?*")</f>
+        <v>13.0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="16" t="inlineStr">
@@ -2083,11 +2251,25 @@
     <mergeCell ref="A13:G13"/>
     <mergeCell ref="A22:G22"/>
   </mergeCells>
+  <conditionalFormatting sqref="A6:G20">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$E6="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="E6 E7 E8 E9 E10 E11 E15 E16 E17 E18 E19 E20" type="list">
+    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E15 E16 E17 E18 E19 E20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
       <formula1>"✓,✗,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-tareas-catering/06-eventos-festivos.xlsx
+++ b/astro-site/public/dl/kit-tareas-catering/06-eventos-festivos.xlsx
@@ -594,7 +594,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -664,7 +664,14 @@
     <row r="13">
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-catering · info@aichef.pro</t>
+          <t>Diseñado por John Guerrero — chef y consultor gastronómico desde 2010, en cocina desde los 17 años · johnguerrero.es</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Versión 2.0 · agosto 2026 · aichef.pro/kit-tareas-catering · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -689,7 +696,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -823,7 +830,7 @@
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>Confirmar horario: cocktail, banquete, barra libre, tarta</t>
+          <t>Recoger POR ESCRITO alérgenos e intolerancias de cada comensal y situarlos en el plano de asientos; cerrar con cocina los platos alternativos y quién los sirve</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
@@ -842,7 +849,7 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>Coordinar con florista, DJ, fotógrafo los accesos y timing</t>
+          <t>Confirmar horario: cocktail, banquete, barra libre, tarta</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
@@ -861,12 +868,12 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>Preparar tarta nupcial o coordinar con pastelería externa</t>
-        </is>
-      </c>
-      <c r="C11" s="14" t="inlineStr">
-        <is>
-          <t>Producción</t>
+          <t>Coordinar con florista, DJ, fotógrafo los accesos y timing</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>Admin</t>
         </is>
       </c>
       <c r="D11" s="11" t="n"/>
@@ -874,77 +881,77 @@
       <c r="F11" s="11" t="n"/>
       <c r="G11" s="13" t="n"/>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>Preparar tarta nupcial o coordinar con pastelería externa</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="inlineStr">
+        <is>
+          <t>Producción</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="n"/>
+      <c r="E12" s="12" t="n"/>
+      <c r="F12" s="11" t="n"/>
+      <c r="G12" s="13" t="n"/>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>Día de la boda</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>Tarea</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C15" s="7" t="inlineStr">
         <is>
           <t>Zona</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D15" s="7" t="inlineStr">
         <is>
           <t>Responsable</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="E15" s="7" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="F15" s="7" t="inlineStr">
         <is>
           <t>Hora</t>
         </is>
       </c>
-      <c r="G14" s="7" t="inlineStr">
+      <c r="G15" s="7" t="inlineStr">
         <is>
           <t>Notas</t>
         </is>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>Cocktail de bienvenida: timing, canapés, bebidas</t>
-        </is>
-      </c>
-      <c r="C15" s="15" t="inlineStr">
-        <is>
-          <t>Servicio</t>
-        </is>
-      </c>
-      <c r="D15" s="11" t="n"/>
-      <c r="E15" s="12" t="n"/>
-      <c r="F15" s="11" t="n"/>
-      <c r="G15" s="13" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>Servicio de mesa: coordinar pases con protocolo nupcial</t>
+          <t>Cocktail de bienvenida: timing, canapés, bebidas</t>
         </is>
       </c>
       <c r="C16" s="15" t="inlineStr">
@@ -959,11 +966,11 @@
     </row>
     <row r="17">
       <c r="A17" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>Corte de tarta: coordinar con fotógrafo y DJ</t>
+          <t>Servicio de mesa: coordinar pases con protocolo nupcial</t>
         </is>
       </c>
       <c r="C17" s="15" t="inlineStr">
@@ -978,11 +985,11 @@
     </row>
     <row r="18">
       <c r="A18" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Barra libre: controlar horario de inicio y fin</t>
+          <t>Corte de tarta: coordinar con fotógrafo y DJ</t>
         </is>
       </c>
       <c r="C18" s="15" t="inlineStr">
@@ -997,11 +1004,11 @@
     </row>
     <row r="19">
       <c r="A19" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Servicio de recena/snack (si aplica)</t>
+          <t>Barra libre: controlar horario de inicio y fin</t>
         </is>
       </c>
       <c r="C19" s="15" t="inlineStr">
@@ -1016,11 +1023,11 @@
     </row>
     <row r="20">
       <c r="A20" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Verificar que novios y mesa principal están atendidos en todo momento</t>
+          <t>Servicio de recena/snack (si aplica)</t>
         </is>
       </c>
       <c r="C20" s="15" t="inlineStr">
@@ -1034,34 +1041,53 @@
       <c r="G20" s="13" t="n"/>
     </row>
     <row r="21">
-      <c r="B21" s="20" t="inlineStr">
+      <c r="A21" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>Verificar que novios y mesa principal están atendidos en todo momento</t>
+        </is>
+      </c>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>Servicio</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="n"/>
+      <c r="E21" s="12" t="n"/>
+      <c r="F21" s="11" t="n"/>
+      <c r="G21" s="13" t="n"/>
+    </row>
+    <row r="22">
+      <c r="B22" s="20" t="inlineStr">
         <is>
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="C21">
-        <f>COUNTIF(E6:E20,"✓")</f>
-        <v>1.0</v>
-      </c>
-      <c r="D21" t="inlineStr">
+      <c r="C22">
+        <f>COUNTIFS(B6:B21,"?*",E6:E21,"✓")-COUNTIFS(B6:B21,"Tarea",E6:E21,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="D22" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="E21">
-        <f>COUNTIF(B6:B20,"?*")</f>
+      <c r="E22">
+        <f>COUNTIF(B6:B21,"?*")-COUNTIF(B6:B21,"Tarea")-COUNTIF(E6:E21,"N/A")</f>
         <v>13.0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="16" t="inlineStr">
-        <is>
-          <t>Firma responsable: _________________  Fecha: ___/___/______</t>
-        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="16" t="inlineStr">
+        <is>
+          <t>Firma responsable: _________________  Fecha: ___/___/______</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="16" t="inlineStr">
         <is>
           <t>© 2026 AI Chef Pro · aichef.pro</t>
         </is>
@@ -1072,18 +1098,18 @@
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A14:G14"/>
     <mergeCell ref="A23:G23"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="A24:G24"/>
   </mergeCells>
-  <conditionalFormatting sqref="A6:G20">
+  <conditionalFormatting sqref="A6:G21">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$E6="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E15 E16 E17 E18 E19 E20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
-      <formula1>"✓,✗,—"</formula1>
+    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E12 E16 E17 E18 E19 E20 E21" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." prompt="Marca ✓ si completada" type="list" errorStyle="stop">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
@@ -1240,7 +1266,7 @@
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>Confirmar restricciones dietéticas de asistentes</t>
+          <t>Confirmar POR ESCRITO alérgenos, intolerancias y dietas especiales de los asistentes, y pasarlos a cocina y a sala</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
@@ -1419,8 +1445,8 @@
         </is>
       </c>
       <c r="C19">
-        <f>COUNTIF(E6:E18,"✓")</f>
-        <v>1.0</v>
+        <f>COUNTIFS(B6:B18,"?*",E6:E18,"✓")-COUNTIFS(B6:B18,"Tarea",E6:E18,"✓")</f>
+        <v>0.0</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1428,8 +1454,8 @@
         </is>
       </c>
       <c r="E19">
-        <f>COUNTIF(B6:B18,"?*")</f>
-        <v>11.0</v>
+        <f>COUNTIF(B6:B18,"?*")-COUNTIF(B6:B18,"Tarea")-COUNTIF(E6:E18,"N/A")</f>
+        <v>10.0</v>
       </c>
     </row>
     <row r="20">
@@ -1461,8 +1487,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E6 E7 E8 E9 E10 E14 E15 E16 E17 E18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
-      <formula1>"✓,✗,—"</formula1>
+    <dataValidation sqref="E6 E7 E8 E9 E10 E14 E15 E16 E17 E18" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." prompt="Marca ✓ si completada" type="list" errorStyle="stop">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
@@ -1485,7 +1511,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1619,12 +1645,12 @@
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>Montar barra de cocktails con 3-4 opciones + refrescos + agua</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>Montaje</t>
+          <t>Ceviche, tartar y cualquier pescado que se sirva crudo o semicrudo — prevención de ANISAKIS: usar sólo pescado con congelación previa acreditada (≥24 h a −20 °C, o 15 h a −35 °C) y anotar el lote</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>Producción</t>
         </is>
       </c>
       <c r="D9" s="11" t="n"/>
@@ -1638,12 +1664,12 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>Calcular personal: 1 camarero / 20 invitados para pase de bandejas</t>
-        </is>
-      </c>
-      <c r="C10" s="10" t="inlineStr">
-        <is>
-          <t>Admin</t>
+          <t>Cada camarero debe saber los alérgenos de la bandeja que pasa: ficha de alérgenos por bandeja y repaso en el briefing</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>Servicio</t>
         </is>
       </c>
       <c r="D10" s="11" t="n"/>
@@ -1651,96 +1677,96 @@
       <c r="F10" s="11" t="n"/>
       <c r="G10" s="13" t="n"/>
     </row>
-    <row r="11"/>
+    <row r="11">
+      <c r="A11" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>Montar barra de cocktails con 3-4 opciones + refrescos + agua</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>Montaje</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="n"/>
+      <c r="E11" s="12" t="n"/>
+      <c r="F11" s="11" t="n"/>
+      <c r="G11" s="13" t="n"/>
+    </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>Calcular personal: 1 camarero / 20 invitados para pase de bandejas</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="n"/>
+      <c r="E12" s="12" t="n"/>
+      <c r="F12" s="11" t="n"/>
+      <c r="G12" s="13" t="n"/>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>Durante el cocktail</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>Tarea</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
+      <c r="C15" s="7" t="inlineStr">
         <is>
           <t>Zona</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D15" s="7" t="inlineStr">
         <is>
           <t>Responsable</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
+      <c r="E15" s="7" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F13" s="7" t="inlineStr">
+      <c r="F15" s="7" t="inlineStr">
         <is>
           <t>Hora</t>
         </is>
       </c>
-      <c r="G13" s="7" t="inlineStr">
+      <c r="G15" s="7" t="inlineStr">
         <is>
           <t>Notas</t>
         </is>
       </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="B14" s="9" t="inlineStr">
-        <is>
-          <t>Salida de bandejas cada 10-15 min con rotación de oferta</t>
-        </is>
-      </c>
-      <c r="C14" s="15" t="inlineStr">
-        <is>
-          <t>Servicio</t>
-        </is>
-      </c>
-      <c r="D14" s="11" t="n"/>
-      <c r="E14" s="12" t="n"/>
-      <c r="F14" s="11" t="n"/>
-      <c r="G14" s="13" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>Reponer estaciones de acción según ritmo de consumo</t>
-        </is>
-      </c>
-      <c r="C15" s="15" t="inlineStr">
-        <is>
-          <t>Servicio</t>
-        </is>
-      </c>
-      <c r="D15" s="11" t="n"/>
-      <c r="E15" s="12" t="n"/>
-      <c r="F15" s="11" t="n"/>
-      <c r="G15" s="13" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>Controlar flujo de bebidas: no dejar a nadie sin copa</t>
+          <t>Salida de bandejas cada 10-15 min con rotación de oferta</t>
         </is>
       </c>
       <c r="C16" s="15" t="inlineStr">
@@ -1755,11 +1781,11 @@
     </row>
     <row r="17">
       <c r="A17" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>Recoger cristalería y servilletas usadas de forma continua</t>
+          <t>Reponer estaciones de acción según ritmo de consumo</t>
         </is>
       </c>
       <c r="C17" s="15" t="inlineStr">
@@ -1774,16 +1800,16 @@
     </row>
     <row r="18">
       <c r="A18" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Mantener zonas limpias y presentables durante todo el evento</t>
-        </is>
-      </c>
-      <c r="C18" s="18" t="inlineStr">
-        <is>
-          <t>Limpieza</t>
+          <t>Controlar flujo de bebidas: no dejar a nadie sin copa</t>
+        </is>
+      </c>
+      <c r="C18" s="15" t="inlineStr">
+        <is>
+          <t>Servicio</t>
         </is>
       </c>
       <c r="D18" s="11" t="n"/>
@@ -1792,34 +1818,72 @@
       <c r="G18" s="13" t="n"/>
     </row>
     <row r="19">
-      <c r="B19" s="20" t="inlineStr">
+      <c r="A19" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>Recoger cristalería y servilletas usadas de forma continua</t>
+        </is>
+      </c>
+      <c r="C19" s="15" t="inlineStr">
+        <is>
+          <t>Servicio</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="n"/>
+      <c r="E19" s="12" t="n"/>
+      <c r="F19" s="11" t="n"/>
+      <c r="G19" s="13" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>Mantener zonas limpias y presentables durante todo el evento</t>
+        </is>
+      </c>
+      <c r="C20" s="18" t="inlineStr">
+        <is>
+          <t>Limpieza</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="n"/>
+      <c r="E20" s="12" t="n"/>
+      <c r="F20" s="11" t="n"/>
+      <c r="G20" s="13" t="n"/>
+    </row>
+    <row r="21">
+      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="C19">
-        <f>COUNTIF(E6:E18,"✓")</f>
-        <v>1.0</v>
-      </c>
-      <c r="D19" t="inlineStr">
+      <c r="C21">
+        <f>COUNTIFS(B6:B20,"?*",E6:E20,"✓")-COUNTIFS(B6:B20,"Tarea",E6:E20,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="D21" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="E19">
-        <f>COUNTIF(B6:B18,"?*")</f>
-        <v>11.0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="16" t="inlineStr">
+      <c r="E21">
+        <f>COUNTIF(B6:B20,"?*")-COUNTIF(B6:B20,"Tarea")-COUNTIF(E6:E20,"N/A")</f>
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>Firma responsable: _________________  Fecha: ___/___/______</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="16" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="16" t="inlineStr">
         <is>
           <t>© 2026 AI Chef Pro · aichef.pro</t>
         </is>
@@ -1827,21 +1891,21 @@
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="A1:G1"/>
     <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A20:G20"/>
+    <mergeCell ref="A14:G14"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A23:G23"/>
+    <mergeCell ref="A22:G22"/>
   </mergeCells>
-  <conditionalFormatting sqref="A6:G18">
+  <conditionalFormatting sqref="A6:G20">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$E6="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E6 E7 E8 E9 E10 E14 E15 E16 E17 E18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
-      <formula1>"✓,✗,—"</formula1>
+    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E12 E16 E17 E18 E19 E20" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." prompt="Marca ✓ si completada" type="list" errorStyle="stop">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
@@ -2119,7 +2183,7 @@
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>Duplicar controles de temperatura (alimentos se calientan más rápido)</t>
+          <t>Duplicar los controles de temperatura: al aire libre los alimentos se calientan mucho más rápido. Máximo 2 h entre 5 °C y 65 °C, y con más de 30 °C de ambiente, 1 h</t>
         </is>
       </c>
       <c r="C16" s="14" t="inlineStr">
@@ -2215,8 +2279,8 @@
         </is>
       </c>
       <c r="C21">
-        <f>COUNTIF(E6:E20,"✓")</f>
-        <v>1.0</v>
+        <f>COUNTIFS(B6:B20,"?*",E6:E20,"✓")-COUNTIFS(B6:B20,"Tarea",E6:E20,"✓")</f>
+        <v>0.0</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2224,8 +2288,8 @@
         </is>
       </c>
       <c r="E21">
-        <f>COUNTIF(B6:B20,"?*")</f>
-        <v>13.0</v>
+        <f>COUNTIF(B6:B20,"?*")-COUNTIF(B6:B20,"Tarea")-COUNTIF(E6:E20,"N/A")</f>
+        <v>12.0</v>
       </c>
     </row>
     <row r="22">
@@ -2257,8 +2321,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E15 E16 E17 E18 E19 E20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
-      <formula1>"✓,✗,—"</formula1>
+    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E15 E16 E17 E18 E19 E20" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." prompt="Marca ✓ si completada" type="list" errorStyle="stop">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>

--- a/astro-site/public/dl/kit-tareas-catering/06-eventos-festivos.xlsx
+++ b/astro-site/public/dl/kit-tareas-catering/06-eventos-festivos.xlsx
@@ -1891,10 +1891,10 @@
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="A4:G4"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A2:G2"/>
     <mergeCell ref="A14:G14"/>
-    <mergeCell ref="A2:G2"/>
     <mergeCell ref="A23:G23"/>
     <mergeCell ref="A22:G22"/>
   </mergeCells>
